--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.533505153046864</v>
+        <v>1.224194587370115</v>
       </c>
       <c r="D2" t="n">
-        <v>7.363256911680256</v>
+        <v>1.196529248148042</v>
       </c>
       <c r="E2" t="n">
-        <v>11.90099692000902</v>
+        <v>1.933911999501467</v>
       </c>
       <c r="F2" t="n">
-        <v>11.88868314649271</v>
+        <v>1.931911011305065</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.96713317007043</v>
+        <v>2.594659140136445</v>
       </c>
       <c r="D3" t="n">
-        <v>16.17038767836776</v>
+        <v>2.627687997734762</v>
       </c>
       <c r="E3" t="n">
-        <v>11.90099692000902</v>
+        <v>1.933911999501467</v>
       </c>
       <c r="F3" t="n">
-        <v>11.88868314649271</v>
+        <v>1.931911011305065</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.13086234021603</v>
+        <v>5.383765130285105</v>
       </c>
       <c r="D4" t="n">
-        <v>33.25243727260629</v>
+        <v>5.403521056798523</v>
       </c>
       <c r="E4" t="n">
-        <v>11.90099692000902</v>
+        <v>1.933911999501467</v>
       </c>
       <c r="F4" t="n">
-        <v>11.88868314649271</v>
+        <v>1.931911011305065</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.98799497809628</v>
+        <v>5.360549183940646</v>
       </c>
       <c r="D5" t="n">
-        <v>32.91491579729096</v>
+        <v>5.348673817059781</v>
       </c>
       <c r="E5" t="n">
-        <v>11.90099692000902</v>
+        <v>1.933911999501467</v>
       </c>
       <c r="F5" t="n">
-        <v>11.88868314649271</v>
+        <v>1.931911011305065</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.41814943542056</v>
+        <v>3.480449283255841</v>
       </c>
       <c r="D6" t="n">
-        <v>21.5846840315102</v>
+        <v>3.507511155120407</v>
       </c>
       <c r="E6" t="n">
-        <v>11.90099692000902</v>
+        <v>1.933911999501467</v>
       </c>
       <c r="F6" t="n">
-        <v>11.88868314649271</v>
+        <v>1.931911011305065</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>44.86936497732406</v>
+        <v>7.29127180881516</v>
       </c>
       <c r="D7" t="n">
-        <v>44.70992985038664</v>
+        <v>7.26536360068783</v>
       </c>
       <c r="E7" t="n">
-        <v>11.90099692000902</v>
+        <v>1.933911999501467</v>
       </c>
       <c r="F7" t="n">
-        <v>11.88868314649271</v>
+        <v>1.931911011305065</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>22.76834760121302</v>
+        <v>3.699856485197115</v>
       </c>
       <c r="D8" t="n">
-        <v>22.64153334989353</v>
+        <v>3.679249169357699</v>
       </c>
       <c r="E8" t="n">
-        <v>11.90099692000902</v>
+        <v>1.933911999501467</v>
       </c>
       <c r="F8" t="n">
-        <v>11.88868314649271</v>
+        <v>1.931911011305065</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>25.93443441383725</v>
+        <v>4.214345592248553</v>
       </c>
       <c r="D9" t="n">
-        <v>25.76479755139199</v>
+        <v>4.186779602101199</v>
       </c>
       <c r="E9" t="n">
-        <v>11.90099692000902</v>
+        <v>1.933911999501467</v>
       </c>
       <c r="F9" t="n">
-        <v>11.88868314649271</v>
+        <v>1.931911011305065</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>14.06374661000072</v>
+        <v>2.285358824125117</v>
       </c>
       <c r="D10" t="n">
-        <v>13.86952595364062</v>
+        <v>2.253797967466601</v>
       </c>
       <c r="E10" t="n">
-        <v>11.90099692000902</v>
+        <v>1.933911999501467</v>
       </c>
       <c r="F10" t="n">
-        <v>11.88868314649271</v>
+        <v>1.931911011305065</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>40.77726986109918</v>
+        <v>6.626306352428617</v>
       </c>
       <c r="D11" t="n">
-        <v>40.94516299012903</v>
+        <v>6.653588985895968</v>
       </c>
       <c r="E11" t="n">
-        <v>11.90099692000902</v>
+        <v>1.933911999501467</v>
       </c>
       <c r="F11" t="n">
-        <v>11.88868314649271</v>
+        <v>1.931911011305065</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>18.96920863445393</v>
+        <v>3.082496403098764</v>
       </c>
       <c r="D12" t="n">
-        <v>18.96745255110959</v>
+        <v>3.082211039555308</v>
       </c>
       <c r="E12" t="n">
-        <v>11.90099692000902</v>
+        <v>1.933911999501467</v>
       </c>
       <c r="F12" t="n">
-        <v>11.88868314649271</v>
+        <v>1.931911011305065</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>44.70516375867057</v>
+        <v>7.264589110783969</v>
       </c>
       <c r="D13" t="n">
-        <v>44.51456341453701</v>
+        <v>7.233616554862264</v>
       </c>
       <c r="E13" t="n">
-        <v>11.90099692000902</v>
+        <v>1.933911999501467</v>
       </c>
       <c r="F13" t="n">
-        <v>11.88868314649271</v>
+        <v>1.931911011305065</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>38.75116547589847</v>
+        <v>6.297064389833502</v>
       </c>
       <c r="D14" t="n">
-        <v>38.77834790846939</v>
+        <v>6.301481535126277</v>
       </c>
       <c r="E14" t="n">
-        <v>11.90099692000902</v>
+        <v>1.933911999501467</v>
       </c>
       <c r="F14" t="n">
-        <v>11.88868314649271</v>
+        <v>1.931911011305065</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>38.38155881415577</v>
+        <v>6.237003307300314</v>
       </c>
       <c r="D15" t="n">
-        <v>38.26135373522787</v>
+        <v>6.21746998197453</v>
       </c>
       <c r="E15" t="n">
-        <v>11.90099692000902</v>
+        <v>1.933911999501467</v>
       </c>
       <c r="F15" t="n">
-        <v>11.88868314649271</v>
+        <v>1.931911011305065</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>47.7471674853598</v>
+        <v>7.758914716370969</v>
       </c>
       <c r="D16" t="n">
-        <v>47.59330996756179</v>
+        <v>7.73391286972879</v>
       </c>
       <c r="E16" t="n">
-        <v>11.90099692000902</v>
+        <v>1.933911999501467</v>
       </c>
       <c r="F16" t="n">
-        <v>11.88868314649271</v>
+        <v>1.931911011305065</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>33.53433280689537</v>
+        <v>5.449329081120498</v>
       </c>
       <c r="D17" t="n">
-        <v>33.49920515900359</v>
+        <v>5.443620838338084</v>
       </c>
       <c r="E17" t="n">
-        <v>11.90099692000902</v>
+        <v>1.933911999501467</v>
       </c>
       <c r="F17" t="n">
-        <v>11.88868314649271</v>
+        <v>1.931911011305065</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
